--- a/artfynd/A 40512-2019 artfynd.xlsx
+++ b/artfynd/A 40512-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -877,6 +877,210 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121540391</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78608</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ramsele, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>579494</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7049438</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121540392</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98016</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ramsele, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>579479</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7049450</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40512-2019 artfynd.xlsx
+++ b/artfynd/A 40512-2019 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>121540392</v>
       </c>
       <c r="B5" t="n">
-        <v>98016</v>
+        <v>98021</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 40512-2019 artfynd.xlsx
+++ b/artfynd/A 40512-2019 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121540391</v>
+        <v>121540392</v>
       </c>
       <c r="B4" t="n">
-        <v>78608</v>
+        <v>98022</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579494</v>
+        <v>579479</v>
       </c>
       <c r="R4" t="n">
-        <v>7049438</v>
+        <v>7049450</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121540392</v>
+        <v>121540391</v>
       </c>
       <c r="B5" t="n">
-        <v>98021</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579479</v>
+        <v>579494</v>
       </c>
       <c r="R5" t="n">
-        <v>7049450</v>
+        <v>7049438</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 40512-2019 artfynd.xlsx
+++ b/artfynd/A 40512-2019 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121540392</v>
+        <v>121540391</v>
       </c>
       <c r="B4" t="n">
-        <v>98022</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579479</v>
+        <v>579494</v>
       </c>
       <c r="R4" t="n">
-        <v>7049450</v>
+        <v>7049438</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121540391</v>
+        <v>121540392</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>98022</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579494</v>
+        <v>579479</v>
       </c>
       <c r="R5" t="n">
-        <v>7049438</v>
+        <v>7049450</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 40512-2019 artfynd.xlsx
+++ b/artfynd/A 40512-2019 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121540391</v>
+        <v>121540392</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>98030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579494</v>
+        <v>579479</v>
       </c>
       <c r="R4" t="n">
-        <v>7049438</v>
+        <v>7049450</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121540392</v>
+        <v>121540391</v>
       </c>
       <c r="B5" t="n">
-        <v>98022</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579479</v>
+        <v>579494</v>
       </c>
       <c r="R5" t="n">
-        <v>7049450</v>
+        <v>7049438</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 40512-2019 artfynd.xlsx
+++ b/artfynd/A 40512-2019 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121540391</v>
+        <v>121540392</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>98030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579494</v>
+        <v>579479</v>
       </c>
       <c r="R4" t="n">
-        <v>7049438</v>
+        <v>7049450</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121540392</v>
+        <v>121540391</v>
       </c>
       <c r="B5" t="n">
-        <v>98030</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579479</v>
+        <v>579494</v>
       </c>
       <c r="R5" t="n">
-        <v>7049450</v>
+        <v>7049438</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 40512-2019 artfynd.xlsx
+++ b/artfynd/A 40512-2019 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121540392</v>
+        <v>121540391</v>
       </c>
       <c r="B4" t="n">
-        <v>98030</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579479</v>
+        <v>579494</v>
       </c>
       <c r="R4" t="n">
-        <v>7049450</v>
+        <v>7049438</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121540391</v>
+        <v>121540392</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>98030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579494</v>
+        <v>579479</v>
       </c>
       <c r="R5" t="n">
-        <v>7049438</v>
+        <v>7049450</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
